--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16BA2D2-E058-43EE-A231-BF21C791E930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C00E20-C742-4F2C-908C-F024C95911AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="15060" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12255" yWindow="1005" windowWidth="19575" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="107">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -454,6 +454,38 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5533,7 +5565,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H453"/>
+  <dimension ref="A2:H470"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -10540,7 +10572,7 @@
     </row>
     <row r="426" spans="1:3">
       <c r="A426">
-        <f t="shared" ref="A426:A452" si="13">A425+1</f>
+        <f t="shared" ref="A426:A444" si="13">A425+1</f>
         <v>112</v>
       </c>
       <c r="B426" t="s">
@@ -10862,6 +10894,200 @@
         <v>96</v>
       </c>
       <c r="C453">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3">
+      <c r="A454">
+        <v>104</v>
+      </c>
+      <c r="B454" t="s">
+        <v>100</v>
+      </c>
+      <c r="C454">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3">
+      <c r="A455">
+        <v>105</v>
+      </c>
+      <c r="B455" t="s">
+        <v>99</v>
+      </c>
+      <c r="C455">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3">
+      <c r="A456">
+        <v>106</v>
+      </c>
+      <c r="B456" t="s">
+        <v>100</v>
+      </c>
+      <c r="C456">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3">
+      <c r="A457">
+        <v>107</v>
+      </c>
+      <c r="B457" t="s">
+        <v>101</v>
+      </c>
+      <c r="C457">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3">
+      <c r="A458">
+        <v>108</v>
+      </c>
+      <c r="B458" t="s">
+        <v>102</v>
+      </c>
+      <c r="C458">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3">
+      <c r="A459">
+        <v>112</v>
+      </c>
+      <c r="B459" t="s">
+        <v>99</v>
+      </c>
+      <c r="C459">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3">
+      <c r="A460">
+        <v>114</v>
+      </c>
+      <c r="B460" t="s">
+        <v>100</v>
+      </c>
+      <c r="C460">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3">
+      <c r="A461">
+        <v>116</v>
+      </c>
+      <c r="B461" t="s">
+        <v>102</v>
+      </c>
+      <c r="C461">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3">
+      <c r="A462">
+        <v>127</v>
+      </c>
+      <c r="B462" t="s">
+        <v>102</v>
+      </c>
+      <c r="C462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3">
+      <c r="A463">
+        <v>131</v>
+      </c>
+      <c r="B463" t="s">
+        <v>103</v>
+      </c>
+      <c r="C463">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3">
+      <c r="A464">
+        <f t="shared" ref="A464:A470" si="14">A463+1</f>
+        <v>132</v>
+      </c>
+      <c r="B464" t="s">
+        <v>104</v>
+      </c>
+      <c r="C464">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3">
+      <c r="A465">
+        <f t="shared" si="14"/>
+        <v>133</v>
+      </c>
+      <c r="B465" t="s">
+        <v>105</v>
+      </c>
+      <c r="C465">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3">
+      <c r="A466">
+        <f t="shared" si="14"/>
+        <v>134</v>
+      </c>
+      <c r="B466" t="s">
+        <v>106</v>
+      </c>
+      <c r="C466">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3">
+      <c r="A467">
+        <f t="shared" si="14"/>
+        <v>135</v>
+      </c>
+      <c r="B467" t="s">
+        <v>106</v>
+      </c>
+      <c r="C467">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3">
+      <c r="A468">
+        <f t="shared" si="14"/>
+        <v>136</v>
+      </c>
+      <c r="B468" t="s">
+        <v>105</v>
+      </c>
+      <c r="C468">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3">
+      <c r="A469">
+        <f t="shared" si="14"/>
+        <v>137</v>
+      </c>
+      <c r="B469" t="s">
+        <v>103</v>
+      </c>
+      <c r="C469">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3">
+      <c r="A470">
+        <f t="shared" si="14"/>
+        <v>138</v>
+      </c>
+      <c r="B470" t="s">
+        <v>104</v>
+      </c>
+      <c r="C470">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C00E20-C742-4F2C-908C-F024C95911AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D7C35D-FC16-4B79-97CE-394D8CAE2A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12255" yWindow="1005" windowWidth="19575" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1095" windowWidth="19575" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="111">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -482,6 +482,22 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -5565,7 +5581,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H470"/>
+  <dimension ref="A2:H478"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -11009,7 +11025,7 @@
     </row>
     <row r="464" spans="1:3">
       <c r="A464">
-        <f t="shared" ref="A464:A470" si="14">A463+1</f>
+        <f t="shared" ref="A464:A478" si="14">A463+1</f>
         <v>132</v>
       </c>
       <c r="B464" t="s">
@@ -11088,6 +11104,102 @@
         <v>104</v>
       </c>
       <c r="C470">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3">
+      <c r="A471">
+        <f t="shared" si="14"/>
+        <v>139</v>
+      </c>
+      <c r="B471" t="s">
+        <v>107</v>
+      </c>
+      <c r="C471">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3">
+      <c r="A472">
+        <f t="shared" si="14"/>
+        <v>140</v>
+      </c>
+      <c r="B472" t="s">
+        <v>108</v>
+      </c>
+      <c r="C472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3">
+      <c r="A473">
+        <f t="shared" si="14"/>
+        <v>141</v>
+      </c>
+      <c r="B473" t="s">
+        <v>108</v>
+      </c>
+      <c r="C473">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3">
+      <c r="A474">
+        <f t="shared" si="14"/>
+        <v>142</v>
+      </c>
+      <c r="B474" t="s">
+        <v>109</v>
+      </c>
+      <c r="C474">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3">
+      <c r="A475">
+        <f t="shared" si="14"/>
+        <v>143</v>
+      </c>
+      <c r="B475" t="s">
+        <v>108</v>
+      </c>
+      <c r="C475">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3">
+      <c r="A476">
+        <f t="shared" si="14"/>
+        <v>144</v>
+      </c>
+      <c r="B476" t="s">
+        <v>109</v>
+      </c>
+      <c r="C476">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3">
+      <c r="A477">
+        <f t="shared" si="14"/>
+        <v>145</v>
+      </c>
+      <c r="B477" t="s">
+        <v>107</v>
+      </c>
+      <c r="C477">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3">
+      <c r="A478">
+        <f t="shared" si="14"/>
+        <v>146</v>
+      </c>
+      <c r="B478" t="s">
+        <v>110</v>
+      </c>
+      <c r="C478">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D7C35D-FC16-4B79-97CE-394D8CAE2A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3612DB-31DA-4E2F-BC55-7B10D8202107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1095" windowWidth="19575" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="115">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -502,6 +502,22 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5581,7 +5597,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H478"/>
+  <dimension ref="A2:H486"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -11025,7 +11041,7 @@
     </row>
     <row r="464" spans="1:3">
       <c r="A464">
-        <f t="shared" ref="A464:A478" si="14">A463+1</f>
+        <f t="shared" ref="A464:A486" si="14">A463+1</f>
         <v>132</v>
       </c>
       <c r="B464" t="s">
@@ -11200,6 +11216,102 @@
         <v>110</v>
       </c>
       <c r="C478">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3">
+      <c r="A479">
+        <f t="shared" si="14"/>
+        <v>147</v>
+      </c>
+      <c r="B479" t="s">
+        <v>111</v>
+      </c>
+      <c r="C479">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3">
+      <c r="A480">
+        <f t="shared" si="14"/>
+        <v>148</v>
+      </c>
+      <c r="B480" t="s">
+        <v>112</v>
+      </c>
+      <c r="C480">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3">
+      <c r="A481">
+        <f t="shared" si="14"/>
+        <v>149</v>
+      </c>
+      <c r="B481" t="s">
+        <v>112</v>
+      </c>
+      <c r="C481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3">
+      <c r="A482">
+        <f t="shared" si="14"/>
+        <v>150</v>
+      </c>
+      <c r="B482" t="s">
+        <v>112</v>
+      </c>
+      <c r="C482">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3">
+      <c r="A483">
+        <f t="shared" si="14"/>
+        <v>151</v>
+      </c>
+      <c r="B483" t="s">
+        <v>113</v>
+      </c>
+      <c r="C483">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3">
+      <c r="A484">
+        <f t="shared" si="14"/>
+        <v>152</v>
+      </c>
+      <c r="B484" t="s">
+        <v>112</v>
+      </c>
+      <c r="C484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3">
+      <c r="A485">
+        <f t="shared" si="14"/>
+        <v>153</v>
+      </c>
+      <c r="B485" t="s">
+        <v>114</v>
+      </c>
+      <c r="C485">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3">
+      <c r="A486">
+        <f t="shared" si="14"/>
+        <v>154</v>
+      </c>
+      <c r="B486" t="s">
+        <v>111</v>
+      </c>
+      <c r="C486">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3612DB-31DA-4E2F-BC55-7B10D8202107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1592EE7E-6144-4AE9-BD90-5E447938EF38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1095" windowWidth="19575" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="495" windowWidth="16515" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="119">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -514,6 +514,22 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -5597,7 +5613,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H486"/>
+  <dimension ref="A2:H492"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -11041,7 +11057,7 @@
     </row>
     <row r="464" spans="1:3">
       <c r="A464">
-        <f t="shared" ref="A464:A486" si="14">A463+1</f>
+        <f t="shared" ref="A464:A492" si="14">A463+1</f>
         <v>132</v>
       </c>
       <c r="B464" t="s">
@@ -11312,6 +11328,78 @@
         <v>111</v>
       </c>
       <c r="C486">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3">
+      <c r="A487">
+        <f t="shared" si="14"/>
+        <v>155</v>
+      </c>
+      <c r="B487" t="s">
+        <v>115</v>
+      </c>
+      <c r="C487">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3">
+      <c r="A488">
+        <f t="shared" si="14"/>
+        <v>156</v>
+      </c>
+      <c r="B488" t="s">
+        <v>116</v>
+      </c>
+      <c r="C488">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3">
+      <c r="A489">
+        <f t="shared" si="14"/>
+        <v>157</v>
+      </c>
+      <c r="B489" t="s">
+        <v>116</v>
+      </c>
+      <c r="C489">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3">
+      <c r="A490">
+        <f t="shared" si="14"/>
+        <v>158</v>
+      </c>
+      <c r="B490" t="s">
+        <v>116</v>
+      </c>
+      <c r="C490">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3">
+      <c r="A491">
+        <f t="shared" si="14"/>
+        <v>159</v>
+      </c>
+      <c r="B491" t="s">
+        <v>117</v>
+      </c>
+      <c r="C491">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3">
+      <c r="A492">
+        <f t="shared" si="14"/>
+        <v>160</v>
+      </c>
+      <c r="B492" t="s">
+        <v>118</v>
+      </c>
+      <c r="C492">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1592EE7E-6144-4AE9-BD90-5E447938EF38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974BE999-AAD7-4CF2-B49B-0D7404138E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="495" windowWidth="16515" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="123">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -530,6 +530,22 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -5613,7 +5629,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H492"/>
+  <dimension ref="A2:H499"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -11057,7 +11073,7 @@
     </row>
     <row r="464" spans="1:3">
       <c r="A464">
-        <f t="shared" ref="A464:A492" si="14">A463+1</f>
+        <f t="shared" ref="A464:A499" si="14">A463+1</f>
         <v>132</v>
       </c>
       <c r="B464" t="s">
@@ -11400,6 +11416,90 @@
         <v>118</v>
       </c>
       <c r="C492">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3">
+      <c r="A493">
+        <f t="shared" si="14"/>
+        <v>161</v>
+      </c>
+      <c r="B493" t="s">
+        <v>119</v>
+      </c>
+      <c r="C493">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3">
+      <c r="A494">
+        <f t="shared" si="14"/>
+        <v>162</v>
+      </c>
+      <c r="B494" t="s">
+        <v>120</v>
+      </c>
+      <c r="C494">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3">
+      <c r="A495">
+        <f t="shared" si="14"/>
+        <v>163</v>
+      </c>
+      <c r="B495" t="s">
+        <v>119</v>
+      </c>
+      <c r="C495">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3">
+      <c r="A496">
+        <f t="shared" si="14"/>
+        <v>164</v>
+      </c>
+      <c r="B496" t="s">
+        <v>121</v>
+      </c>
+      <c r="C496">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3">
+      <c r="A497">
+        <f t="shared" si="14"/>
+        <v>165</v>
+      </c>
+      <c r="B497" t="s">
+        <v>121</v>
+      </c>
+      <c r="C497">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3">
+      <c r="A498">
+        <f t="shared" si="14"/>
+        <v>166</v>
+      </c>
+      <c r="B498" t="s">
+        <v>122</v>
+      </c>
+      <c r="C498">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3">
+      <c r="A499">
+        <f t="shared" si="14"/>
+        <v>167</v>
+      </c>
+      <c r="B499" t="s">
+        <v>121</v>
+      </c>
+      <c r="C499">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974BE999-AAD7-4CF2-B49B-0D7404138E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B342C7D-E507-46E4-9B01-2AEADDCEE9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="495" windowWidth="16515" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="126">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -550,6 +550,18 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5629,7 +5641,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H499"/>
+  <dimension ref="A2:H507"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -11073,7 +11085,7 @@
     </row>
     <row r="464" spans="1:3">
       <c r="A464">
-        <f t="shared" ref="A464:A499" si="14">A463+1</f>
+        <f t="shared" ref="A464:A507" si="14">A463+1</f>
         <v>132</v>
       </c>
       <c r="B464" t="s">
@@ -11500,6 +11512,102 @@
         <v>121</v>
       </c>
       <c r="C499">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3">
+      <c r="A500">
+        <f t="shared" si="14"/>
+        <v>168</v>
+      </c>
+      <c r="B500" t="s">
+        <v>123</v>
+      </c>
+      <c r="C500">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3">
+      <c r="A501">
+        <f t="shared" si="14"/>
+        <v>169</v>
+      </c>
+      <c r="B501" t="s">
+        <v>124</v>
+      </c>
+      <c r="C501">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3">
+      <c r="A502">
+        <f t="shared" si="14"/>
+        <v>170</v>
+      </c>
+      <c r="B502" t="s">
+        <v>123</v>
+      </c>
+      <c r="C502">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3">
+      <c r="A503">
+        <f t="shared" si="14"/>
+        <v>171</v>
+      </c>
+      <c r="B503" t="s">
+        <v>124</v>
+      </c>
+      <c r="C503">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3">
+      <c r="A504">
+        <f t="shared" si="14"/>
+        <v>172</v>
+      </c>
+      <c r="B504" t="s">
+        <v>125</v>
+      </c>
+      <c r="C504">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3">
+      <c r="A505">
+        <f t="shared" si="14"/>
+        <v>173</v>
+      </c>
+      <c r="B505" t="s">
+        <v>125</v>
+      </c>
+      <c r="C505">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3">
+      <c r="A506">
+        <f t="shared" si="14"/>
+        <v>174</v>
+      </c>
+      <c r="B506" t="s">
+        <v>123</v>
+      </c>
+      <c r="C506">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3">
+      <c r="A507">
+        <f t="shared" si="14"/>
+        <v>175</v>
+      </c>
+      <c r="B507" t="s">
+        <v>124</v>
+      </c>
+      <c r="C507">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B342C7D-E507-46E4-9B01-2AEADDCEE9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6AEA06D-3C2E-43F0-AD39-957842F91356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="495" windowWidth="16515" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="130">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -562,6 +562,22 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5641,7 +5657,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H507"/>
+  <dimension ref="A2:H512"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -11085,7 +11101,7 @@
     </row>
     <row r="464" spans="1:3">
       <c r="A464">
-        <f t="shared" ref="A464:A507" si="14">A463+1</f>
+        <f t="shared" ref="A464:A512" si="14">A463+1</f>
         <v>132</v>
       </c>
       <c r="B464" t="s">
@@ -11608,6 +11624,66 @@
         <v>124</v>
       </c>
       <c r="C507">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3">
+      <c r="A508">
+        <f t="shared" si="14"/>
+        <v>176</v>
+      </c>
+      <c r="B508" t="s">
+        <v>126</v>
+      </c>
+      <c r="C508">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3">
+      <c r="A509">
+        <f t="shared" si="14"/>
+        <v>177</v>
+      </c>
+      <c r="B509" t="s">
+        <v>127</v>
+      </c>
+      <c r="C509">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3">
+      <c r="A510">
+        <f t="shared" si="14"/>
+        <v>178</v>
+      </c>
+      <c r="B510" t="s">
+        <v>128</v>
+      </c>
+      <c r="C510">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3">
+      <c r="A511">
+        <f t="shared" si="14"/>
+        <v>179</v>
+      </c>
+      <c r="B511" t="s">
+        <v>129</v>
+      </c>
+      <c r="C511">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3">
+      <c r="A512">
+        <f t="shared" si="14"/>
+        <v>180</v>
+      </c>
+      <c r="B512" t="s">
+        <v>127</v>
+      </c>
+      <c r="C512">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6AEA06D-3C2E-43F0-AD39-957842F91356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5C8753-D2E4-4FAF-A751-2439F1085A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="495" windowWidth="16515" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4545" yWindow="285" windowWidth="16515" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="133">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -578,6 +578,18 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5657,7 +5669,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H512"/>
+  <dimension ref="A2:H517"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -11101,7 +11113,7 @@
     </row>
     <row r="464" spans="1:3">
       <c r="A464">
-        <f t="shared" ref="A464:A512" si="14">A463+1</f>
+        <f t="shared" ref="A464:A517" si="14">A463+1</f>
         <v>132</v>
       </c>
       <c r="B464" t="s">
@@ -11685,6 +11697,66 @@
       </c>
       <c r="C512">
         <v>1</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3">
+      <c r="A513">
+        <f t="shared" si="14"/>
+        <v>181</v>
+      </c>
+      <c r="B513" t="s">
+        <v>130</v>
+      </c>
+      <c r="C513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3">
+      <c r="A514">
+        <f t="shared" si="14"/>
+        <v>182</v>
+      </c>
+      <c r="B514" t="s">
+        <v>131</v>
+      </c>
+      <c r="C514">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3">
+      <c r="A515">
+        <f t="shared" si="14"/>
+        <v>183</v>
+      </c>
+      <c r="B515" t="s">
+        <v>132</v>
+      </c>
+      <c r="C515">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3">
+      <c r="A516">
+        <f t="shared" si="14"/>
+        <v>184</v>
+      </c>
+      <c r="B516" t="s">
+        <v>132</v>
+      </c>
+      <c r="C516">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3">
+      <c r="A517">
+        <f t="shared" si="14"/>
+        <v>185</v>
+      </c>
+      <c r="B517" t="s">
+        <v>130</v>
+      </c>
+      <c r="C517">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5C8753-D2E4-4FAF-A751-2439F1085A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34AA524-A96A-41F8-BE0F-A733C7FFEDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4545" yWindow="285" windowWidth="16515" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6030" yWindow="630" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="137">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -590,6 +590,22 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5669,7 +5685,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H517"/>
+  <dimension ref="A2:H522"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -11113,7 +11129,7 @@
     </row>
     <row r="464" spans="1:3">
       <c r="A464">
-        <f t="shared" ref="A464:A517" si="14">A463+1</f>
+        <f t="shared" ref="A464:A522" si="14">A463+1</f>
         <v>132</v>
       </c>
       <c r="B464" t="s">
@@ -11757,6 +11773,66 @@
       </c>
       <c r="C517">
         <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3">
+      <c r="A518">
+        <f t="shared" si="14"/>
+        <v>186</v>
+      </c>
+      <c r="B518" t="s">
+        <v>133</v>
+      </c>
+      <c r="C518">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3">
+      <c r="A519">
+        <f t="shared" si="14"/>
+        <v>187</v>
+      </c>
+      <c r="B519" t="s">
+        <v>134</v>
+      </c>
+      <c r="C519">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3">
+      <c r="A520">
+        <f t="shared" si="14"/>
+        <v>188</v>
+      </c>
+      <c r="B520" t="s">
+        <v>135</v>
+      </c>
+      <c r="C520">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3">
+      <c r="A521">
+        <f t="shared" si="14"/>
+        <v>189</v>
+      </c>
+      <c r="B521" t="s">
+        <v>133</v>
+      </c>
+      <c r="C521">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3">
+      <c r="A522">
+        <f t="shared" si="14"/>
+        <v>190</v>
+      </c>
+      <c r="B522" t="s">
+        <v>136</v>
+      </c>
+      <c r="C522">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34AA524-A96A-41F8-BE0F-A733C7FFEDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4A75B2-8518-41B6-BAF1-336CE80847E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6030" yWindow="630" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="0" windowWidth="13710" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="141">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -606,6 +606,22 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5685,7 +5701,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H522"/>
+  <dimension ref="A2:H527"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -11129,7 +11145,7 @@
     </row>
     <row r="464" spans="1:3">
       <c r="A464">
-        <f t="shared" ref="A464:A522" si="14">A463+1</f>
+        <f t="shared" ref="A464:A527" si="14">A463+1</f>
         <v>132</v>
       </c>
       <c r="B464" t="s">
@@ -11832,6 +11848,66 @@
         <v>136</v>
       </c>
       <c r="C522">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3">
+      <c r="A523">
+        <f t="shared" si="14"/>
+        <v>191</v>
+      </c>
+      <c r="B523" t="s">
+        <v>137</v>
+      </c>
+      <c r="C523">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3">
+      <c r="A524">
+        <f t="shared" si="14"/>
+        <v>192</v>
+      </c>
+      <c r="B524" t="s">
+        <v>138</v>
+      </c>
+      <c r="C524">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3">
+      <c r="A525">
+        <f t="shared" si="14"/>
+        <v>193</v>
+      </c>
+      <c r="B525" t="s">
+        <v>139</v>
+      </c>
+      <c r="C525">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3">
+      <c r="A526">
+        <f t="shared" si="14"/>
+        <v>194</v>
+      </c>
+      <c r="B526" t="s">
+        <v>137</v>
+      </c>
+      <c r="C526">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3">
+      <c r="A527">
+        <f t="shared" si="14"/>
+        <v>195</v>
+      </c>
+      <c r="B527" t="s">
+        <v>140</v>
+      </c>
+      <c r="C527">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4A75B2-8518-41B6-BAF1-336CE80847E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0BBB71-0F08-4EFF-B1AD-4BFEF75C40BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="0" windowWidth="13710" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="144">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -622,6 +622,18 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5701,7 +5713,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H527"/>
+  <dimension ref="A2:H532"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -11145,7 +11157,7 @@
     </row>
     <row r="464" spans="1:3">
       <c r="A464">
-        <f t="shared" ref="A464:A527" si="14">A463+1</f>
+        <f t="shared" ref="A464:A528" si="14">A463+1</f>
         <v>132</v>
       </c>
       <c r="B464" t="s">
@@ -11908,6 +11920,66 @@
         <v>140</v>
       </c>
       <c r="C527">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3">
+      <c r="A528">
+        <f t="shared" si="14"/>
+        <v>196</v>
+      </c>
+      <c r="B528" t="s">
+        <v>141</v>
+      </c>
+      <c r="C528">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3">
+      <c r="A529">
+        <f t="shared" ref="A529:A532" si="15">A528+1</f>
+        <v>197</v>
+      </c>
+      <c r="B529" t="s">
+        <v>142</v>
+      </c>
+      <c r="C529">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3">
+      <c r="A530">
+        <f t="shared" si="15"/>
+        <v>198</v>
+      </c>
+      <c r="B530" t="s">
+        <v>142</v>
+      </c>
+      <c r="C530">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3">
+      <c r="A531">
+        <f t="shared" si="15"/>
+        <v>199</v>
+      </c>
+      <c r="B531" t="s">
+        <v>143</v>
+      </c>
+      <c r="C531">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3">
+      <c r="A532">
+        <f t="shared" si="15"/>
+        <v>200</v>
+      </c>
+      <c r="B532" t="s">
+        <v>142</v>
+      </c>
+      <c r="C532">
         <v>1</v>
       </c>
     </row>
